--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20241.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20241.xlsx
@@ -820,25 +820,25 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -855,25 +855,25 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="J3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -887,25 +887,25 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>2.9</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -922,25 +922,25 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -954,25 +954,25 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -989,25 +989,25 @@
         <v>10</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1021,25 +1021,25 @@
         <v>10</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1050,25 +1050,25 @@
         <v>70</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F9">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>1.4</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J9">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1349,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20241.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20241.xlsx
@@ -855,25 +855,25 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -887,25 +887,25 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1050,25 +1050,25 @@
         <v>70</v>
       </c>
       <c r="E9">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>1.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20241.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20241.xlsx
@@ -536,10 +536,10 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -551,7 +551,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -568,10 +568,10 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -583,7 +583,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -603,28 +603,28 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>25</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I5" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -635,28 +635,28 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>25</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I6" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -731,28 +731,28 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E9">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I9" s="2">
         <v>9</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
   </sheetData>
@@ -852,10 +852,10 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -884,10 +884,10 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -919,28 +919,28 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>25</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I5" s="2">
         <v>9.4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -951,28 +951,28 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>25</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I6" s="2">
         <v>9.4</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1047,28 +1047,28 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E9">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I9" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
   </sheetData>
@@ -1168,10 +1168,10 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1200,10 +1200,10 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1235,28 +1235,28 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>25</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I5" s="2">
         <v>9.4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1267,28 +1267,28 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>25</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I6" s="2">
         <v>9.4</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1363,28 +1363,28 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E9">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I9" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20241.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20241.xlsx
@@ -606,25 +606,25 @@
         <v>29</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -638,25 +638,25 @@
         <v>29</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -734,25 +734,25 @@
         <v>78</v>
       </c>
       <c r="E9">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
         <v>9</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -922,25 +922,25 @@
         <v>29</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
         <v>9.4</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -954,25 +954,25 @@
         <v>29</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
         <v>9.4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1050,25 +1050,25 @@
         <v>78</v>
       </c>
       <c r="E9">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1238,25 +1238,25 @@
         <v>29</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1270,25 +1270,25 @@
         <v>29</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1366,25 +1366,25 @@
         <v>78</v>
       </c>
       <c r="E9">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
         <v>9.4</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
